--- a/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2487736_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2487736_PROCESSED_CHRONO.xlsx
@@ -565,13 +565,13 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>6.1901</v>
+        <v>6.7545</v>
       </c>
       <c r="E2" t="n">
-        <v>6.7769</v>
+        <v>7.4776</v>
       </c>
       <c r="F2" t="n">
-        <v>-0.5868</v>
+        <v>-0.7231</v>
       </c>
       <c r="G2" t="n">
         <v>3.7405</v>
@@ -610,13 +610,13 @@
         <v>0.9702</v>
       </c>
       <c r="S2" t="n">
-        <v>-0.4071</v>
+        <v>0.1573</v>
       </c>
       <c r="T2" t="n">
-        <v>-0.7268</v>
+        <v>-0.0261</v>
       </c>
       <c r="U2" t="n">
-        <v>0.3197</v>
+        <v>0.1834</v>
       </c>
       <c r="V2" t="n">
         <v>2.0806</v>
@@ -643,13 +643,13 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>5.1197</v>
+        <v>5.3838</v>
       </c>
       <c r="E3" t="n">
-        <v>5.925</v>
+        <v>6.3254</v>
       </c>
       <c r="F3" t="n">
-        <v>-0.8053</v>
+        <v>-0.9416</v>
       </c>
       <c r="G3" t="n">
         <v>0.6748</v>
@@ -688,13 +688,13 @@
         <v>2.1344</v>
       </c>
       <c r="S3" t="n">
-        <v>-0.3342</v>
+        <v>-0.0701</v>
       </c>
       <c r="T3" t="n">
-        <v>-0.4229</v>
+        <v>-0.0225</v>
       </c>
       <c r="U3" t="n">
-        <v>0.0886</v>
+        <v>-0.0476</v>
       </c>
       <c r="V3" t="n">
         <v>2.6447</v>
@@ -721,13 +721,13 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>3.8331</v>
+        <v>3.2875</v>
       </c>
       <c r="E4" t="n">
-        <v>4.9115</v>
+        <v>4.6112</v>
       </c>
       <c r="F4" t="n">
-        <v>-1.0784</v>
+        <v>-1.3237</v>
       </c>
       <c r="G4" t="n">
         <v>3.3748</v>
@@ -766,13 +766,13 @@
         <v>2.3284</v>
       </c>
       <c r="S4" t="n">
-        <v>0.127</v>
+        <v>-0.4186</v>
       </c>
       <c r="T4" t="n">
-        <v>0.2445</v>
+        <v>-0.0558</v>
       </c>
       <c r="U4" t="n">
-        <v>-0.1175</v>
+        <v>-0.3628</v>
       </c>
       <c r="V4" t="n">
         <v>-1.0269</v>
@@ -799,13 +799,13 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>1.9172</v>
+        <v>2.6634</v>
       </c>
       <c r="E5" t="n">
-        <v>3.1261</v>
+        <v>3.9269</v>
       </c>
       <c r="F5" t="n">
-        <v>-1.2089</v>
+        <v>-1.2634</v>
       </c>
       <c r="G5" t="n">
         <v>0.8901</v>
@@ -844,13 +844,13 @@
         <v>1.5523</v>
       </c>
       <c r="S5" t="n">
-        <v>-0.255</v>
+        <v>0.4912</v>
       </c>
       <c r="T5" t="n">
-        <v>-0.7268</v>
+        <v>0.074</v>
       </c>
       <c r="U5" t="n">
-        <v>0.4718</v>
+        <v>0.4172</v>
       </c>
       <c r="V5" t="n">
         <v>0.894</v>
@@ -865,7 +865,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>M. KHIVRENKO</t>
+          <t>F. QUERO CARMONA</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -877,73 +877,73 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>1.1297</v>
+        <v>0.3761</v>
       </c>
       <c r="E6" t="n">
-        <v>0.4189</v>
+        <v>-0.109</v>
       </c>
       <c r="F6" t="n">
-        <v>0.7108</v>
+        <v>0.4851</v>
       </c>
       <c r="G6" t="n">
-        <v>-0.9513</v>
+        <v>1.1131</v>
       </c>
       <c r="H6" t="n">
-        <v>-1.2655</v>
+        <v>1.8216</v>
       </c>
       <c r="I6" t="n">
-        <v>0.3142</v>
+        <v>-0.7085</v>
       </c>
       <c r="J6" t="n">
-        <v>-0.349</v>
+        <v>0.9243</v>
       </c>
       <c r="K6" t="n">
-        <v>-0.552</v>
+        <v>1.6271</v>
       </c>
       <c r="L6" t="n">
-        <v>0.203</v>
+        <v>-0.7029</v>
       </c>
       <c r="M6" t="n">
-        <v>-0.6022999999999999</v>
+        <v>0.1889</v>
       </c>
       <c r="N6" t="n">
-        <v>-0.7135</v>
+        <v>0.1944</v>
       </c>
       <c r="O6" t="n">
-        <v>0.1112</v>
+        <v>-0.0056</v>
       </c>
       <c r="P6" t="n">
+        <v>-0.194</v>
+      </c>
+      <c r="Q6" t="n">
         <v>-0.9702</v>
       </c>
-      <c r="Q6" t="n">
-        <v>-2.1344</v>
-      </c>
       <c r="R6" t="n">
-        <v>1.1642</v>
+        <v>0.7761</v>
       </c>
       <c r="S6" t="n">
-        <v>1.5825</v>
+        <v>0.1063</v>
       </c>
       <c r="T6" t="n">
-        <v>1.3963</v>
+        <v>-0.0631</v>
       </c>
       <c r="U6" t="n">
-        <v>0.1862</v>
+        <v>0.1694</v>
       </c>
       <c r="V6" t="n">
-        <v>1.4686</v>
+        <v>-0.6492</v>
       </c>
       <c r="W6" t="n">
-        <v>1.506</v>
+        <v>0</v>
       </c>
       <c r="X6" t="n">
-        <v>-0.0373</v>
+        <v>-0.6492</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>M. NIMAGA</t>
+          <t>M. KHIVRENKO</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -955,73 +955,73 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>0.424</v>
+        <v>-0.0075</v>
       </c>
       <c r="E7" t="n">
-        <v>1.0251</v>
+        <v>-0.5821</v>
       </c>
       <c r="F7" t="n">
-        <v>-0.6011</v>
+        <v>0.5745</v>
       </c>
       <c r="G7" t="n">
-        <v>-2.4144</v>
+        <v>-0.9513</v>
       </c>
       <c r="H7" t="n">
-        <v>-1.0636</v>
+        <v>-1.2655</v>
       </c>
       <c r="I7" t="n">
-        <v>-1.3508</v>
+        <v>0.3142</v>
       </c>
       <c r="J7" t="n">
-        <v>-0.4779</v>
+        <v>-0.349</v>
       </c>
       <c r="K7" t="n">
-        <v>-0.762</v>
+        <v>-0.552</v>
       </c>
       <c r="L7" t="n">
-        <v>0.2842</v>
+        <v>0.203</v>
       </c>
       <c r="M7" t="n">
-        <v>-1.9366</v>
+        <v>-0.6022999999999999</v>
       </c>
       <c r="N7" t="n">
-        <v>-0.3015</v>
+        <v>-0.7135</v>
       </c>
       <c r="O7" t="n">
-        <v>-1.635</v>
+        <v>0.1112</v>
       </c>
       <c r="P7" t="n">
         <v>-0.9702</v>
       </c>
       <c r="Q7" t="n">
-        <v>-1.9403</v>
+        <v>-2.1344</v>
       </c>
       <c r="R7" t="n">
-        <v>0.9702</v>
+        <v>1.1642</v>
       </c>
       <c r="S7" t="n">
-        <v>3.1967</v>
+        <v>0.4453</v>
       </c>
       <c r="T7" t="n">
-        <v>2.5493</v>
+        <v>0.3953</v>
       </c>
       <c r="U7" t="n">
-        <v>0.6474</v>
+        <v>0.0499</v>
       </c>
       <c r="V7" t="n">
-        <v>0.6119</v>
+        <v>1.4686</v>
       </c>
       <c r="W7" t="n">
-        <v>0.894</v>
+        <v>1.506</v>
       </c>
       <c r="X7" t="n">
-        <v>-0.2821</v>
+        <v>-0.0373</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>F. QUERO CARMONA</t>
+          <t>B. FERNANDEZ SHEPHARD</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1033,67 +1033,67 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>0.07580000000000001</v>
+        <v>-0.517</v>
       </c>
       <c r="E8" t="n">
-        <v>-0.4093</v>
+        <v>2.1631</v>
       </c>
       <c r="F8" t="n">
-        <v>0.4851</v>
+        <v>-2.6801</v>
       </c>
       <c r="G8" t="n">
-        <v>1.1131</v>
+        <v>1.608</v>
       </c>
       <c r="H8" t="n">
-        <v>1.8216</v>
+        <v>0.8716</v>
       </c>
       <c r="I8" t="n">
-        <v>-0.7085</v>
+        <v>0.7363</v>
       </c>
       <c r="J8" t="n">
-        <v>0.9243</v>
+        <v>3.7066</v>
       </c>
       <c r="K8" t="n">
-        <v>1.6271</v>
+        <v>1.7301</v>
       </c>
       <c r="L8" t="n">
-        <v>-0.7029</v>
+        <v>1.9765</v>
       </c>
       <c r="M8" t="n">
-        <v>0.1889</v>
+        <v>-2.0987</v>
       </c>
       <c r="N8" t="n">
-        <v>0.1944</v>
+        <v>-0.8585</v>
       </c>
       <c r="O8" t="n">
-        <v>-0.0056</v>
+        <v>-1.2402</v>
       </c>
       <c r="P8" t="n">
-        <v>-0.194</v>
+        <v>0.7761</v>
       </c>
       <c r="Q8" t="n">
-        <v>-0.9702</v>
+        <v>-1.1642</v>
       </c>
       <c r="R8" t="n">
-        <v>0.7761</v>
+        <v>1.9403</v>
       </c>
       <c r="S8" t="n">
-        <v>-0.194</v>
+        <v>0.2064</v>
       </c>
       <c r="T8" t="n">
-        <v>-0.3634</v>
+        <v>0.2804</v>
       </c>
       <c r="U8" t="n">
-        <v>0.1694</v>
+        <v>-0.074</v>
       </c>
       <c r="V8" t="n">
-        <v>-0.6492</v>
+        <v>-3.1075</v>
       </c>
       <c r="W8" t="n">
-        <v>0</v>
+        <v>-0.6597</v>
       </c>
       <c r="X8" t="n">
-        <v>-0.6492</v>
+        <v>-2.4477</v>
       </c>
     </row>
     <row r="9">
@@ -1111,13 +1111,13 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-0.3116</v>
+        <v>-0.5757</v>
       </c>
       <c r="E9" t="n">
-        <v>0.632</v>
+        <v>0.2316</v>
       </c>
       <c r="F9" t="n">
-        <v>-0.9436</v>
+        <v>-0.8074</v>
       </c>
       <c r="G9" t="n">
         <v>1.6155</v>
@@ -1156,13 +1156,13 @@
         <v>0.5821</v>
       </c>
       <c r="S9" t="n">
-        <v>1.2191</v>
+        <v>0.955</v>
       </c>
       <c r="T9" t="n">
-        <v>0.7896</v>
+        <v>0.3892</v>
       </c>
       <c r="U9" t="n">
-        <v>0.4296</v>
+        <v>0.5659</v>
       </c>
       <c r="V9" t="n">
         <v>-1.788</v>
@@ -1177,7 +1177,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>B. FERNANDEZ SHEPHARD</t>
+          <t>M. NIMAGA</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1189,67 +1189,67 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-1.3535</v>
+        <v>-1.4229</v>
       </c>
       <c r="E10" t="n">
-        <v>1.7627</v>
+        <v>-0.5765</v>
       </c>
       <c r="F10" t="n">
-        <v>-3.1162</v>
+        <v>-0.8464</v>
       </c>
       <c r="G10" t="n">
-        <v>1.608</v>
+        <v>-2.4144</v>
       </c>
       <c r="H10" t="n">
-        <v>0.8716</v>
+        <v>-1.0636</v>
       </c>
       <c r="I10" t="n">
-        <v>0.7363</v>
+        <v>-1.3508</v>
       </c>
       <c r="J10" t="n">
-        <v>3.7066</v>
+        <v>-0.4779</v>
       </c>
       <c r="K10" t="n">
-        <v>1.7301</v>
+        <v>-0.762</v>
       </c>
       <c r="L10" t="n">
-        <v>1.9765</v>
+        <v>0.2842</v>
       </c>
       <c r="M10" t="n">
-        <v>-2.0987</v>
+        <v>-1.9366</v>
       </c>
       <c r="N10" t="n">
-        <v>-0.8585</v>
+        <v>-0.3015</v>
       </c>
       <c r="O10" t="n">
-        <v>-1.2402</v>
+        <v>-1.635</v>
       </c>
       <c r="P10" t="n">
-        <v>0.7761</v>
+        <v>-0.9702</v>
       </c>
       <c r="Q10" t="n">
-        <v>-1.1642</v>
+        <v>-1.9403</v>
       </c>
       <c r="R10" t="n">
-        <v>1.9403</v>
+        <v>0.9702</v>
       </c>
       <c r="S10" t="n">
-        <v>-0.6301</v>
+        <v>1.3498</v>
       </c>
       <c r="T10" t="n">
-        <v>-0.12</v>
+        <v>0.9477</v>
       </c>
       <c r="U10" t="n">
-        <v>-0.5101</v>
+        <v>0.4021</v>
       </c>
       <c r="V10" t="n">
-        <v>-3.1075</v>
+        <v>0.6119</v>
       </c>
       <c r="W10" t="n">
-        <v>-0.6597</v>
+        <v>0.894</v>
       </c>
       <c r="X10" t="n">
-        <v>-2.4477</v>
+        <v>-0.2821</v>
       </c>
     </row>
     <row r="11">
@@ -1267,13 +1267,13 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-1.9846</v>
+        <v>-1.6937</v>
       </c>
       <c r="E11" t="n">
-        <v>-0.1804</v>
+        <v>-0.0803</v>
       </c>
       <c r="F11" t="n">
-        <v>-1.8042</v>
+        <v>-1.6134</v>
       </c>
       <c r="G11" t="n">
         <v>-0.4516</v>
@@ -1312,13 +1312,13 @@
         <v>0.194</v>
       </c>
       <c r="S11" t="n">
-        <v>-0.5031</v>
+        <v>-0.2123</v>
       </c>
       <c r="T11" t="n">
-        <v>-0.3634</v>
+        <v>-0.2633</v>
       </c>
       <c r="U11" t="n">
-        <v>-0.1397</v>
+        <v>0.051</v>
       </c>
       <c r="V11" t="n">
         <v>-1.2239</v>
@@ -1345,13 +1345,13 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-10.1696</v>
+        <v>-9.3782</v>
       </c>
       <c r="E12" t="n">
-        <v>-6.2529</v>
+        <v>-5.6523</v>
       </c>
       <c r="F12" t="n">
-        <v>-3.9167</v>
+        <v>-3.7259</v>
       </c>
       <c r="G12" t="n">
         <v>-3.4724</v>
@@ -1390,13 +1390,13 @@
         <v>1.9403</v>
       </c>
       <c r="S12" t="n">
-        <v>-0.8912</v>
+        <v>-0.0998</v>
       </c>
       <c r="T12" t="n">
-        <v>-0.7874</v>
+        <v>-0.1868</v>
       </c>
       <c r="U12" t="n">
-        <v>-0.1038</v>
+        <v>0.08690000000000001</v>
       </c>
       <c r="V12" t="n">
         <v>-3.6716</v>
@@ -1423,13 +1423,13 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>4.870299999999999</v>
+        <v>4.870300000000002</v>
       </c>
       <c r="E13" t="n">
         <v>17.7356</v>
       </c>
       <c r="F13" t="n">
-        <v>-12.8653</v>
+        <v>-12.8654</v>
       </c>
       <c r="G13" t="n">
         <v>5.7271</v>
@@ -1453,13 +1453,13 @@
         <v>-13.7521</v>
       </c>
       <c r="N13" t="n">
-        <v>-5.4376</v>
+        <v>-5.437599999999999</v>
       </c>
       <c r="O13" t="n">
         <v>-8.314299999999999</v>
       </c>
       <c r="P13" t="n">
-        <v>-9.999999999932285e-05</v>
+        <v>-9.999999999887876e-05</v>
       </c>
       <c r="Q13" t="n">
         <v>-14.5525</v>
@@ -1468,13 +1468,13 @@
         <v>14.5525</v>
       </c>
       <c r="S13" t="n">
-        <v>2.9106</v>
+        <v>2.9105</v>
       </c>
       <c r="T13" t="n">
-        <v>1.469000000000001</v>
+        <v>1.469</v>
       </c>
       <c r="U13" t="n">
-        <v>1.4416</v>
+        <v>1.4414</v>
       </c>
       <c r="V13" t="n">
         <v>-3.767300000000001</v>
@@ -1489,7 +1489,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>M. NIANG</t>
+          <t>D. RODRIGUEZ GARCIA</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1501,67 +1501,67 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>2.3423</v>
+        <v>3.0735</v>
       </c>
       <c r="E14" t="n">
-        <v>2.8456</v>
+        <v>3.5011</v>
       </c>
       <c r="F14" t="n">
-        <v>-0.5033</v>
+        <v>-0.4276</v>
       </c>
       <c r="G14" t="n">
-        <v>-0.7486</v>
+        <v>-3.2529</v>
       </c>
       <c r="H14" t="n">
-        <v>1.4253</v>
+        <v>-2.381</v>
       </c>
       <c r="I14" t="n">
-        <v>-2.1739</v>
+        <v>-0.8719</v>
       </c>
       <c r="J14" t="n">
-        <v>2.1791</v>
+        <v>-0.1861</v>
       </c>
       <c r="K14" t="n">
-        <v>2.5623</v>
+        <v>-1.244</v>
       </c>
       <c r="L14" t="n">
-        <v>-0.3832</v>
+        <v>1.0579</v>
       </c>
       <c r="M14" t="n">
-        <v>-2.9277</v>
+        <v>-3.0668</v>
       </c>
       <c r="N14" t="n">
         <v>-1.137</v>
       </c>
       <c r="O14" t="n">
-        <v>-1.7908</v>
+        <v>-1.9298</v>
       </c>
       <c r="P14" t="n">
-        <v>-1.3582</v>
+        <v>0.5821</v>
       </c>
       <c r="Q14" t="n">
-        <v>-3.8806</v>
+        <v>-1.9403</v>
       </c>
       <c r="R14" t="n">
         <v>2.5224</v>
       </c>
       <c r="S14" t="n">
-        <v>3.3477</v>
+        <v>-1.1945</v>
       </c>
       <c r="T14" t="n">
-        <v>2.4293</v>
+        <v>-0.7739</v>
       </c>
       <c r="U14" t="n">
-        <v>0.9184</v>
+        <v>-0.4206</v>
       </c>
       <c r="V14" t="n">
-        <v>1.1015</v>
+        <v>6.9388</v>
       </c>
       <c r="W14" t="n">
-        <v>2.1179</v>
+        <v>6.4014</v>
       </c>
       <c r="X14" t="n">
-        <v>-1.0164</v>
+        <v>0.5373</v>
       </c>
     </row>
     <row r="15">
@@ -1579,10 +1579,10 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>2.1627</v>
+        <v>0.9615</v>
       </c>
       <c r="E15" t="n">
-        <v>1.6565</v>
+        <v>0.4553</v>
       </c>
       <c r="F15" t="n">
         <v>0.5063</v>
@@ -1624,10 +1624,10 @@
         <v>1.9403</v>
       </c>
       <c r="S15" t="n">
-        <v>1.1653</v>
+        <v>-0.0359</v>
       </c>
       <c r="T15" t="n">
-        <v>1.458</v>
+        <v>0.2568</v>
       </c>
       <c r="U15" t="n">
         <v>-0.2927</v>
@@ -1645,7 +1645,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>D. RODRIGUEZ GARCIA</t>
+          <t>M. RODRÍGUEZ RIVEROL</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1657,67 +1657,67 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>2.1092</v>
+        <v>0.9046</v>
       </c>
       <c r="E16" t="n">
-        <v>2.7003</v>
+        <v>3.1132</v>
       </c>
       <c r="F16" t="n">
-        <v>-0.5911</v>
+        <v>-2.2087</v>
       </c>
       <c r="G16" t="n">
-        <v>-3.2529</v>
+        <v>-0.2572</v>
       </c>
       <c r="H16" t="n">
-        <v>-2.381</v>
+        <v>0.131</v>
       </c>
       <c r="I16" t="n">
-        <v>-0.8719</v>
+        <v>-0.3882</v>
       </c>
       <c r="J16" t="n">
-        <v>-0.1861</v>
+        <v>1.8128</v>
       </c>
       <c r="K16" t="n">
-        <v>-1.244</v>
+        <v>0.4325</v>
       </c>
       <c r="L16" t="n">
-        <v>1.0579</v>
+        <v>1.3803</v>
       </c>
       <c r="M16" t="n">
-        <v>-3.0668</v>
+        <v>-2.07</v>
       </c>
       <c r="N16" t="n">
-        <v>-1.137</v>
+        <v>-0.3015</v>
       </c>
       <c r="O16" t="n">
-        <v>-1.9298</v>
+        <v>-1.7685</v>
       </c>
       <c r="P16" t="n">
-        <v>0.5821</v>
+        <v>0.7761</v>
       </c>
       <c r="Q16" t="n">
-        <v>-1.9403</v>
+        <v>0</v>
       </c>
       <c r="R16" t="n">
-        <v>2.5224</v>
+        <v>0.7761</v>
       </c>
       <c r="S16" t="n">
-        <v>-2.1588</v>
+        <v>-0.1517</v>
       </c>
       <c r="T16" t="n">
-        <v>-1.5747</v>
+        <v>0.0765</v>
       </c>
       <c r="U16" t="n">
-        <v>-0.5841</v>
+        <v>-0.2282</v>
       </c>
       <c r="V16" t="n">
-        <v>6.9388</v>
+        <v>0.5373</v>
       </c>
       <c r="W16" t="n">
-        <v>6.4014</v>
+        <v>1.2239</v>
       </c>
       <c r="X16" t="n">
-        <v>0.5373</v>
+        <v>-0.6866</v>
       </c>
     </row>
     <row r="17">
@@ -1735,13 +1735,13 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>0.3893</v>
+        <v>0.8264</v>
       </c>
       <c r="E17" t="n">
-        <v>1.074</v>
+        <v>1.6746</v>
       </c>
       <c r="F17" t="n">
-        <v>-0.6847</v>
+        <v>-0.8483000000000001</v>
       </c>
       <c r="G17" t="n">
         <v>-1.6587</v>
@@ -1780,13 +1780,13 @@
         <v>2.3284</v>
       </c>
       <c r="S17" t="n">
-        <v>-1.5042</v>
+        <v>-1.0672</v>
       </c>
       <c r="T17" t="n">
-        <v>-1.2719</v>
+        <v>-0.6713</v>
       </c>
       <c r="U17" t="n">
-        <v>-0.2324</v>
+        <v>-0.3959</v>
       </c>
       <c r="V17" t="n">
         <v>1.2239</v>
@@ -1801,7 +1801,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>M. RODRÍGUEZ RIVEROL</t>
+          <t>D. OJEDA DAVILA</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1813,73 +1813,73 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>0.3223</v>
+        <v>0.3447</v>
       </c>
       <c r="E18" t="n">
-        <v>2.6127</v>
+        <v>3.7191</v>
       </c>
       <c r="F18" t="n">
-        <v>-2.2904</v>
+        <v>-3.3743</v>
       </c>
       <c r="G18" t="n">
-        <v>-0.2572</v>
+        <v>2.5119</v>
       </c>
       <c r="H18" t="n">
-        <v>0.131</v>
+        <v>0.2035</v>
       </c>
       <c r="I18" t="n">
-        <v>-0.3882</v>
+        <v>2.3084</v>
       </c>
       <c r="J18" t="n">
-        <v>1.8128</v>
+        <v>3.7031</v>
       </c>
       <c r="K18" t="n">
         <v>0.4325</v>
       </c>
       <c r="L18" t="n">
-        <v>1.3803</v>
+        <v>3.2706</v>
       </c>
       <c r="M18" t="n">
-        <v>-2.07</v>
+        <v>-1.1912</v>
       </c>
       <c r="N18" t="n">
-        <v>-0.3015</v>
+        <v>-0.229</v>
       </c>
       <c r="O18" t="n">
-        <v>-1.7685</v>
+        <v>-0.9621</v>
       </c>
       <c r="P18" t="n">
-        <v>0.7761</v>
+        <v>0.5821</v>
       </c>
       <c r="Q18" t="n">
         <v>0</v>
       </c>
       <c r="R18" t="n">
-        <v>0.7761</v>
+        <v>0.5821</v>
       </c>
       <c r="S18" t="n">
-        <v>-0.734</v>
+        <v>0.1029</v>
       </c>
       <c r="T18" t="n">
-        <v>-0.424</v>
+        <v>0.016</v>
       </c>
       <c r="U18" t="n">
-        <v>-0.31</v>
+        <v>0.08690000000000001</v>
       </c>
       <c r="V18" t="n">
-        <v>0.5373</v>
+        <v>-2.8522</v>
       </c>
       <c r="W18" t="n">
-        <v>1.2239</v>
+        <v>0</v>
       </c>
       <c r="X18" t="n">
-        <v>-0.6866</v>
+        <v>-2.8522</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>D. OJEDA DAVILA</t>
+          <t>M. NIANG</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1891,67 +1891,67 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>-0.3466</v>
+        <v>-0.4684</v>
       </c>
       <c r="E19" t="n">
-        <v>3.2186</v>
+        <v>0.7435</v>
       </c>
       <c r="F19" t="n">
-        <v>-3.5651</v>
+        <v>-1.2119</v>
       </c>
       <c r="G19" t="n">
-        <v>2.5119</v>
+        <v>-0.7486</v>
       </c>
       <c r="H19" t="n">
-        <v>0.2035</v>
+        <v>1.4253</v>
       </c>
       <c r="I19" t="n">
-        <v>2.3084</v>
+        <v>-2.1739</v>
       </c>
       <c r="J19" t="n">
-        <v>3.7031</v>
+        <v>2.1791</v>
       </c>
       <c r="K19" t="n">
-        <v>0.4325</v>
+        <v>2.5623</v>
       </c>
       <c r="L19" t="n">
-        <v>3.2706</v>
+        <v>-0.3832</v>
       </c>
       <c r="M19" t="n">
-        <v>-1.1912</v>
+        <v>-2.9277</v>
       </c>
       <c r="N19" t="n">
-        <v>-0.229</v>
+        <v>-1.137</v>
       </c>
       <c r="O19" t="n">
-        <v>-0.9621</v>
+        <v>-1.7908</v>
       </c>
       <c r="P19" t="n">
-        <v>0.5821</v>
+        <v>-1.3582</v>
       </c>
       <c r="Q19" t="n">
-        <v>0</v>
+        <v>-3.8806</v>
       </c>
       <c r="R19" t="n">
-        <v>0.5821</v>
+        <v>2.5224</v>
       </c>
       <c r="S19" t="n">
-        <v>-0.5884</v>
+        <v>0.5369</v>
       </c>
       <c r="T19" t="n">
-        <v>-0.4845</v>
+        <v>0.3272</v>
       </c>
       <c r="U19" t="n">
-        <v>-0.1038</v>
+        <v>0.2098</v>
       </c>
       <c r="V19" t="n">
-        <v>-2.8522</v>
+        <v>1.1015</v>
       </c>
       <c r="W19" t="n">
-        <v>0</v>
+        <v>2.1179</v>
       </c>
       <c r="X19" t="n">
-        <v>-2.8522</v>
+        <v>-1.0164</v>
       </c>
     </row>
     <row r="20">
@@ -1969,13 +1969,13 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-0.5915</v>
+        <v>-0.7466</v>
       </c>
       <c r="E20" t="n">
-        <v>0.3823</v>
+        <v>-0.0181</v>
       </c>
       <c r="F20" t="n">
-        <v>-0.9738</v>
+        <v>-0.7285</v>
       </c>
       <c r="G20" t="n">
         <v>-0.4783</v>
@@ -2014,13 +2014,13 @@
         <v>1.3582</v>
       </c>
       <c r="S20" t="n">
-        <v>-0.1146</v>
+        <v>-0.2697</v>
       </c>
       <c r="T20" t="n">
-        <v>0.1222</v>
+        <v>-0.2782</v>
       </c>
       <c r="U20" t="n">
-        <v>-0.2369</v>
+        <v>0.008399999999999999</v>
       </c>
       <c r="V20" t="n">
         <v>1.5537</v>
@@ -2047,13 +2047,13 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-1.7226</v>
+        <v>-1.7404</v>
       </c>
       <c r="E21" t="n">
-        <v>-0.4017</v>
+        <v>-0.2015</v>
       </c>
       <c r="F21" t="n">
-        <v>-1.3209</v>
+        <v>-1.5389</v>
       </c>
       <c r="G21" t="n">
         <v>0.6477000000000001</v>
@@ -2092,13 +2092,13 @@
         <v>0.3881</v>
       </c>
       <c r="S21" t="n">
-        <v>0.0476</v>
+        <v>0.0297</v>
       </c>
       <c r="T21" t="n">
-        <v>-0.1817</v>
+        <v>0.0185</v>
       </c>
       <c r="U21" t="n">
-        <v>0.2293</v>
+        <v>0.0112</v>
       </c>
       <c r="V21" t="n">
         <v>-1.8358</v>
@@ -2125,13 +2125,13 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-4.5953</v>
+        <v>-3.622</v>
       </c>
       <c r="E22" t="n">
-        <v>1.0789</v>
+        <v>1.7796</v>
       </c>
       <c r="F22" t="n">
-        <v>-5.6741</v>
+        <v>-5.4016</v>
       </c>
       <c r="G22" t="n">
         <v>-0.5479000000000001</v>
@@ -2170,13 +2170,13 @@
         <v>1.5523</v>
       </c>
       <c r="S22" t="n">
-        <v>-1.928</v>
+        <v>-0.9547</v>
       </c>
       <c r="T22" t="n">
-        <v>-1.2113</v>
+        <v>-0.5106000000000001</v>
       </c>
       <c r="U22" t="n">
-        <v>-0.7167</v>
+        <v>-0.4441</v>
       </c>
       <c r="V22" t="n">
         <v>-3.6716</v>
@@ -2203,13 +2203,13 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-4.9402</v>
+        <v>-4.4036</v>
       </c>
       <c r="E23" t="n">
-        <v>-2.3017</v>
+        <v>-1.9013</v>
       </c>
       <c r="F23" t="n">
-        <v>-2.6385</v>
+        <v>-2.5023</v>
       </c>
       <c r="G23" t="n">
         <v>-2.4808</v>
@@ -2248,13 +2248,13 @@
         <v>0.5821</v>
       </c>
       <c r="S23" t="n">
-        <v>-0.443</v>
+        <v>0.09370000000000001</v>
       </c>
       <c r="T23" t="n">
-        <v>-0.3028</v>
+        <v>0.09760000000000001</v>
       </c>
       <c r="U23" t="n">
-        <v>-0.1402</v>
+        <v>-0.0039</v>
       </c>
       <c r="V23" t="n">
         <v>-1.6283</v>
@@ -2281,19 +2281,19 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>-4.8704</v>
+        <v>-4.8703</v>
       </c>
       <c r="E24" t="n">
         <v>12.8655</v>
       </c>
       <c r="F24" t="n">
-        <v>-17.7356</v>
+        <v>-17.7358</v>
       </c>
       <c r="G24" t="n">
         <v>-5.727</v>
       </c>
       <c r="H24" t="n">
-        <v>0.3625000000000006</v>
+        <v>0.3625000000000004</v>
       </c>
       <c r="I24" t="n">
         <v>-6.089600000000001</v>
@@ -2317,7 +2317,7 @@
         <v>-14.404</v>
       </c>
       <c r="P24" t="n">
-        <v>3.33066907387547e-16</v>
+        <v>-1.110223024625157e-16</v>
       </c>
       <c r="Q24" t="n">
         <v>-14.5524</v>
@@ -2326,7 +2326,7 @@
         <v>14.5524</v>
       </c>
       <c r="S24" t="n">
-        <v>-2.9104</v>
+        <v>-2.9105</v>
       </c>
       <c r="T24" t="n">
         <v>-1.4414</v>
